--- a/python/PythonCoding/file_mgmt/data.xlsx
+++ b/python/PythonCoding/file_mgmt/data.xlsx
@@ -419,7 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Name,;Age</t>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Age</t>
         </is>
       </c>
     </row>
@@ -436,8 +441,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jane Smith,25</t>
+          <t>Jane Smith</t>
         </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
